--- a/Data/National Accounts/PSA-11ESWW_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-11ESWW_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72B4E50-1170-4626-9709-93F36D5BBC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD687A9F-C0BD-4D2D-A9AE-79592DF7D8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESWW" sheetId="1" r:id="rId1"/>
@@ -620,9 +620,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -630,6 +627,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23589,7 +23589,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23599,7 +23599,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -23801,10 +23801,10 @@
         <v>697906.10742185055</v>
       </c>
       <c r="Z12" s="8">
-        <v>732392.11330421316</v>
+        <v>732817.88290599931</v>
       </c>
       <c r="AA12" s="8">
-        <v>749112.62077177363</v>
+        <v>753552.97120409994</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23956,7 +23956,7 @@
         <v>13933.724434594877</v>
       </c>
       <c r="AA13" s="8">
-        <v>14067.502399480672</v>
+        <v>14068.472039146642</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24105,10 +24105,10 @@
         <v>121752.37868424846</v>
       </c>
       <c r="Z14" s="8">
-        <v>139203.98332872367</v>
+        <v>139192.42993366648</v>
       </c>
       <c r="AA14" s="8">
-        <v>151069.64931366695</v>
+        <v>151544.19222499366</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -24257,10 +24257,10 @@
         <v>10274.674659075714</v>
       </c>
       <c r="Z15" s="8">
-        <v>11518.952738769874</v>
+        <v>11449.749093902683</v>
       </c>
       <c r="AA15" s="8">
-        <v>12402.474085634261</v>
+        <v>12480.027180699781</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -24507,10 +24507,10 @@
         <v>844195.92131620785</v>
       </c>
       <c r="Z17" s="12">
-        <v>897048.77380630153</v>
+        <v>897393.7863681633</v>
       </c>
       <c r="AA17" s="12">
-        <v>926652.24657055549</v>
+        <v>931645.66264894011</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -24824,7 +24824,7 @@
     </row>
     <row r="24" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:96" x14ac:dyDescent="0.2">
@@ -24834,7 +24834,7 @@
     </row>
     <row r="27" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:96" x14ac:dyDescent="0.2">
@@ -25036,10 +25036,10 @@
         <v>557186.65910545969</v>
       </c>
       <c r="Z33" s="8">
-        <v>599814.49212255538</v>
+        <v>600219.14244948979</v>
       </c>
       <c r="AA33" s="8">
-        <v>597399.1672044294</v>
+        <v>601507.64091932774</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -25340,10 +25340,10 @@
         <v>106528.95833482558</v>
       </c>
       <c r="Z35" s="8">
-        <v>113306.57005091861</v>
+        <v>113297.00008691402</v>
       </c>
       <c r="AA35" s="8">
-        <v>116315.90453366245</v>
+        <v>116690.26992822967</v>
       </c>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -25492,10 +25492,10 @@
         <v>8845.8507530919123</v>
       </c>
       <c r="Z36" s="8">
-        <v>9706.1035910132032</v>
+        <v>9647.0602195716147</v>
       </c>
       <c r="AA36" s="8">
-        <v>10339.810199254782</v>
+        <v>10405.032613480796</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -25742,10 +25742,10 @@
         <v>684752.72877578472</v>
       </c>
       <c r="Z38" s="12">
-        <v>734556.85213866213</v>
+        <v>734892.88913015032</v>
       </c>
       <c r="AA38" s="12">
-        <v>736242.21161523962</v>
+        <v>740790.27313893114</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -26059,7 +26059,7 @@
     </row>
     <row r="45" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:96" x14ac:dyDescent="0.2">
@@ -26069,7 +26069,7 @@
     </row>
     <row r="48" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:91" x14ac:dyDescent="0.2">
@@ -26188,7 +26188,7 @@
         <v>48</v>
       </c>
       <c r="Z52" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA52" s="17"/>
     </row>
@@ -26269,10 +26269,10 @@
         <v>12.608379483476611</v>
       </c>
       <c r="Y54" s="18">
-        <v>4.9413532158012003</v>
+        <v>5.0023599325011077</v>
       </c>
       <c r="Z54" s="18">
-        <v>2.2829993884184887</v>
+        <v>2.8295008598692135</v>
       </c>
       <c r="AA54" s="18"/>
       <c r="AB54" s="9"/>
@@ -26417,7 +26417,7 @@
         <v>-2.3069595486862227</v>
       </c>
       <c r="Z55" s="18">
-        <v>0.96010198503459776</v>
+        <v>0.96706092605944605</v>
       </c>
       <c r="AA55" s="18"/>
       <c r="AB55" s="9"/>
@@ -26559,10 +26559,10 @@
         <v>17.019447215752308</v>
       </c>
       <c r="Y56" s="18">
-        <v>14.333686810123083</v>
+        <v>14.3241975539935</v>
       </c>
       <c r="Z56" s="18">
-        <v>8.5239414140348799</v>
+        <v>8.8738750355989282</v>
       </c>
       <c r="AA56" s="18"/>
       <c r="AB56" s="9"/>
@@ -26704,10 +26704,10 @@
         <v>8.7821944324509218</v>
       </c>
       <c r="Y57" s="18">
-        <v>12.110145780577881</v>
+        <v>11.436609662273</v>
       </c>
       <c r="Z57" s="18">
-        <v>7.6701534149947292</v>
+        <v>8.9982590740416413</v>
       </c>
       <c r="AA57" s="18"/>
       <c r="AB57" s="9"/>
@@ -26942,10 +26942,10 @@
         <v>13.14719243558531</v>
       </c>
       <c r="Y59" s="18">
-        <v>6.2607329833682854</v>
+        <v>6.3016017619480351</v>
       </c>
       <c r="Z59" s="18">
-        <v>3.3000962298451526</v>
+        <v>3.8168167421124508</v>
       </c>
       <c r="AA59" s="18"/>
       <c r="AB59" s="9"/>
@@ -27245,7 +27245,7 @@
     </row>
     <row r="66" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:91" x14ac:dyDescent="0.2">
@@ -27255,7 +27255,7 @@
     </row>
     <row r="69" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:91" x14ac:dyDescent="0.2">
@@ -27371,7 +27371,7 @@
         <v>48</v>
       </c>
       <c r="Z73" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA73" s="6"/>
     </row>
@@ -27452,10 +27452,10 @@
         <v>5.770464017361661</v>
       </c>
       <c r="Y75" s="18">
-        <v>7.6505480381624551</v>
+        <v>7.72317187441584</v>
       </c>
       <c r="Z75" s="18">
-        <v>-0.40267865312472395</v>
+        <v>0.21467133896788937</v>
       </c>
       <c r="AA75" s="18"/>
       <c r="AB75" s="9"/>
@@ -27742,10 +27742,10 @@
         <v>6.1412080966600513</v>
       </c>
       <c r="Y77" s="18">
-        <v>6.3622247152653699</v>
+        <v>6.3532412762510546</v>
       </c>
       <c r="Z77" s="18">
-        <v>2.6559223188836114</v>
+        <v>2.9950217911441257</v>
       </c>
       <c r="AA77" s="18"/>
       <c r="AB77" s="9"/>
@@ -27887,10 +27887,10 @@
         <v>4.9873573925314219</v>
       </c>
       <c r="Y78" s="18">
-        <v>9.7249305005581874</v>
+        <v>9.0574608236483556</v>
       </c>
       <c r="Z78" s="18">
-        <v>6.5289495655942034</v>
+        <v>7.857029775469158</v>
       </c>
       <c r="AA78" s="18"/>
       <c r="AB78" s="9"/>
@@ -28125,10 +28125,10 @@
         <v>5.798741105972411</v>
       </c>
       <c r="Y80" s="18">
-        <v>7.2733004586806373</v>
+        <v>7.3223746685912658</v>
       </c>
       <c r="Z80" s="18">
-        <v>0.22943894290420985</v>
+        <v>0.80248211623890597</v>
       </c>
       <c r="AA80" s="18"/>
       <c r="AB80" s="9"/>
@@ -28425,7 +28425,7 @@
     </row>
     <row r="86" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:96" x14ac:dyDescent="0.2">
@@ -28435,7 +28435,7 @@
     </row>
     <row r="89" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:96" x14ac:dyDescent="0.2">
@@ -28637,10 +28637,10 @@
         <v>125.25535132917757</v>
       </c>
       <c r="Z95" s="18">
-        <v>122.10310403013224</v>
+        <v>122.09172135286705</v>
       </c>
       <c r="AA95" s="18">
-        <v>125.39565869790175</v>
+        <v>125.27737304423769</v>
       </c>
       <c r="AB95" s="9"/>
       <c r="AC95" s="9"/>
@@ -28792,7 +28792,7 @@
         <v>118.7902556821347</v>
       </c>
       <c r="AA96" s="18">
-        <v>115.42727382683529</v>
+        <v>115.43522995579542</v>
       </c>
       <c r="AB96" s="9"/>
       <c r="AC96" s="9"/>
@@ -28941,10 +28941,10 @@
         <v>114.29040571444898</v>
       </c>
       <c r="Z97" s="18">
-        <v>122.8560561547023</v>
+        <v>122.85623611118316</v>
       </c>
       <c r="AA97" s="18">
-        <v>129.87875554881367</v>
+        <v>129.86874768410502</v>
       </c>
       <c r="AB97" s="9"/>
       <c r="AC97" s="9"/>
@@ -29093,10 +29093,10 @@
         <v>116.15247584280553</v>
       </c>
       <c r="Z98" s="18">
-        <v>118.677413966972</v>
+        <v>118.68640635904643</v>
       </c>
       <c r="AA98" s="18">
-        <v>119.94875966415846</v>
+        <v>119.94222069549896</v>
       </c>
       <c r="AB98" s="9"/>
       <c r="AC98" s="9"/>
@@ -29343,10 +29343,10 @@
         <v>123.28478381173873</v>
       </c>
       <c r="Z100" s="18">
-        <v>122.12108173717857</v>
+        <v>122.1121879993091</v>
       </c>
       <c r="AA100" s="18">
-        <v>125.8624175510904</v>
+        <v>125.7637547940934</v>
       </c>
       <c r="AB100" s="9"/>
       <c r="AC100" s="9"/>
@@ -29464,7 +29464,7 @@
     </row>
     <row r="107" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:96" x14ac:dyDescent="0.2">
@@ -29474,7 +29474,7 @@
     </row>
     <row r="110" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:96" x14ac:dyDescent="0.2">
@@ -29676,10 +29676,10 @@
         <v>82.671106291739363</v>
       </c>
       <c r="Z116" s="18">
-        <v>81.644625653583191</v>
+        <v>81.660681635849286</v>
       </c>
       <c r="AA116" s="18">
-        <v>80.840749433691244</v>
+        <v>80.88407443035041</v>
       </c>
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
@@ -29828,10 +29828,10 @@
         <v>1.6895083464506375</v>
       </c>
       <c r="Z117" s="18">
-        <v>1.5532850432950445</v>
+        <v>1.55268786638093</v>
       </c>
       <c r="AA117" s="18">
-        <v>1.5180994220370208</v>
+        <v>1.5100668208067298</v>
       </c>
       <c r="AB117" s="9"/>
       <c r="AC117" s="9"/>
@@ -29980,10 +29980,10 @@
         <v>14.422289377378316</v>
       </c>
       <c r="Z118" s="18">
-        <v>15.517994940014464</v>
+        <v>15.510741443507348</v>
       </c>
       <c r="AA118" s="18">
-        <v>16.302733832757667</v>
+        <v>16.266290747719403</v>
       </c>
       <c r="AB118" s="9"/>
       <c r="AC118" s="9"/>
@@ -30132,10 +30132,10 @@
         <v>1.2170959844316946</v>
       </c>
       <c r="Z119" s="18">
-        <v>1.2840943631073003</v>
+        <v>1.2758890542624426</v>
       </c>
       <c r="AA119" s="18">
-        <v>1.3384173115140594</v>
+        <v>1.3395680011234556</v>
       </c>
       <c r="AB119" s="9"/>
       <c r="AC119" s="9"/>
@@ -30699,7 +30699,7 @@
     </row>
     <row r="128" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="130" spans="1:96" x14ac:dyDescent="0.2">
@@ -30709,7 +30709,7 @@
     </row>
     <row r="131" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:96" x14ac:dyDescent="0.2">
@@ -30911,10 +30911,10 @@
         <v>81.370491228506623</v>
       </c>
       <c r="Z137" s="18">
-        <v>81.656646504105922</v>
+        <v>81.6743706909362</v>
       </c>
       <c r="AA137" s="18">
-        <v>81.141662048118263</v>
+        <v>81.19810190954253</v>
       </c>
       <c r="AB137" s="9"/>
       <c r="AC137" s="9"/>
@@ -31063,10 +31063,10 @@
         <v>1.7803887549602504</v>
       </c>
       <c r="Z138" s="18">
-        <v>1.5968384666243216</v>
+        <v>1.5961082965517108</v>
       </c>
       <c r="AA138" s="18">
-        <v>1.6553424247647002</v>
+        <v>1.6451794954396348</v>
       </c>
       <c r="AB138" s="9"/>
       <c r="AC138" s="9"/>
@@ -31215,10 +31215,10 @@
         <v>15.5572886179337</v>
       </c>
       <c r="Z139" s="18">
-        <v>15.425160043232399</v>
+        <v>15.416804511609447</v>
       </c>
       <c r="AA139" s="18">
-        <v>15.79859218863278</v>
+        <v>15.752133115055772</v>
       </c>
       <c r="AB139" s="9"/>
       <c r="AC139" s="9"/>
@@ -31367,10 +31367,10 @@
         <v>1.2918313985994199</v>
       </c>
       <c r="Z140" s="18">
-        <v>1.3213549860373481</v>
+        <v>1.3127165009026383</v>
       </c>
       <c r="AA140" s="18">
-        <v>1.4044033384842609</v>
+        <v>1.4045854799620716</v>
       </c>
       <c r="AB140" s="9"/>
       <c r="AC140" s="9"/>
